--- a/data/trans_camb/P1805_2016_2023-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1805_2016_2023-Habitat-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,57</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,93</t>
+          <t>-0,27; 3,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,25</t>
+          <t>-1,88; 1,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,67</t>
+          <t>-0,7; 1,73</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>100,84%</t>
+          <t>104,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-7,62%</t>
+          <t>-5,85%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,34; 412,28</t>
+          <t>-28,72; 425,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 70,37</t>
+          <t>-48,51; 87,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 110,22</t>
+          <t>-26,97; 121,05</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,48</t>
+          <t>-0,67; 2,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,89</t>
+          <t>-1,35; 1,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,29</t>
+          <t>-0,65; 1,48</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 118,36</t>
+          <t>-33,52; 199,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 75,62</t>
+          <t>-31,95; 71,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 62,61</t>
+          <t>-21,11; 73,31</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>2,24</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,09</t>
+          <t>0,69; 4,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,59</t>
+          <t>0,38; 4,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,39</t>
+          <t>0,9; 3,76</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>174,25%</t>
+          <t>162,87%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>103,59%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,53; 550,95</t>
+          <t>28,0; 529,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 151,49</t>
+          <t>7,77; 199,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,61; 210,68</t>
+          <t>30,4; 225,97</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,42</t>
+          <t>0,04; 3,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,37</t>
+          <t>-1,94; 1,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,28</t>
+          <t>-0,42; 2,26</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-7,28%</t>
+          <t>-1,21%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,33; 217,98</t>
+          <t>-1,28; 200,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,92; 32,67</t>
+          <t>-31,53; 42,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 65,67</t>
+          <t>-9,02; 67,72</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,01</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,43</t>
+          <t>0,7; 2,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,27</t>
+          <t>-0,38; 1,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,6</t>
+          <t>0,42; 1,69</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>24,69; 159,33</t>
+          <t>33,6; 157,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 38,12</t>
+          <t>-9,56; 44,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,41; 65,19</t>
+          <t>13,41; 69,32</t>
         </is>
       </c>
     </row>
